--- a/excel_routes/route_RUH_CAI_threats.xlsx
+++ b/excel_routes/route_RUH_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-354</t>
+          <t>flyadeal F3-611</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1529</v>
+        <v>1345</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-892</v>
+        <v>-851</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-254</t>
+          <t>flyadeal F3-615</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1529</v>
+        <v>1345</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-892</v>
+        <v>-851</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1529</v>
+        <v>1437</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-892</v>
+        <v>-759</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-252</t>
+          <t>flyadeal F3-605</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1529</v>
+        <v>1449</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-892</v>
+        <v>-747</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flynas XY-271</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-886</v>
+        <v>-657</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-287</t>
+          <t>flyadeal F3-607</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1539</v>
+        <v>1645</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-882</v>
+        <v>-551</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>flynas XY-265</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1539</v>
+        <v>1729</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-882</v>
+        <v>-467</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-275</t>
+          <t>flynas XY-267</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1539</v>
+        <v>1729</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-882</v>
+        <v>-467</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-263</t>
+          <t>flynas XY-275</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1539</v>
+        <v>1729</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-882</v>
+        <v>-467</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>23-MAR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-271</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1539</v>
+        <v>1843</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-882</v>
+        <v>-353</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1755</v>
+        <v>1175</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2421</v>
+        <v>1664</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-666</v>
+        <v>-489</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-265</t>
+          <t>Nile Air NP-254</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1879</v>
+        <v>1333</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2421</v>
+        <v>1664</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-542</v>
+        <v>-331</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,22 +1095,22 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1879</v>
+        <v>1459</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2421</v>
+        <v>1664</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-542</v>
+        <v>-205</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>Air Arabia Egypt E5-416</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1879</v>
+        <v>1477</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2421</v>
+        <v>1664</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-542</v>
+        <v>-187</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-611</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2149</v>
+        <v>1529</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2421</v>
+        <v>1664</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-272</v>
+        <v>-135</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1216,40 +1216,40 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-615</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2149</v>
+        <v>1333</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-272</v>
+        <v>-563</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,27 +1261,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-607</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2333</v>
+        <v>1335</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-88</v>
+        <v>-561</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,36 +1306,36 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-163</t>
+          <t>flynas XY-263</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1335</v>
+        <v>1459</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-786</v>
+        <v>-437</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,36 +1351,36 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-154</t>
+          <t>flynas XY-269</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1529</v>
+        <v>1459</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-592</v>
+        <v>-437</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,27 +1396,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>Nile Air NP-254</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
         <v>1529</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-592</v>
+        <v>-367</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,27 +1441,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-586</v>
+        <v>-367</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,40 +1486,40 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-263</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-582</v>
+        <v>-361</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,27 +1531,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>flynas XY-265</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>1539</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-582</v>
+        <v>-357</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>20</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,40 +1576,40 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-416</t>
+          <t>flynas XY-267</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1700</v>
+        <v>1539</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-421</v>
+        <v>-357</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,27 +1621,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Air Arabia Egypt E5-416</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1748</v>
+        <v>1651</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-373</v>
+        <v>-245</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-607</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1749</v>
+        <v>1333</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-372</v>
+        <v>-863</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-265</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1879</v>
+        <v>1335</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-242</v>
+        <v>-861</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-267</t>
+          <t>flynas XY-263</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1879</v>
+        <v>1459</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-242</v>
+        <v>-737</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-10</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>flynas XY-269</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1879</v>
+        <v>1459</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-242</v>
+        <v>-737</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-10</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-275</t>
+          <t>Nile Air NP-254</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1879</v>
+        <v>1529</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-242</v>
+        <v>-667</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-271</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1879</v>
+        <v>1529</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-242</v>
+        <v>-667</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-287</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2069</v>
+        <v>1535</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-52</v>
+        <v>-661</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-352</t>
+          <t>flynas XY-265</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-592</v>
+        <v>-657</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>flynas XY-267</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-592</v>
+        <v>-657</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-165</t>
+          <t>Air Arabia Egypt E5-416</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1535</v>
+        <v>1651</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-586</v>
+        <v>-545</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-163</t>
+          <t>flyadeal F3-615</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1535</v>
+        <v>1749</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-586</v>
+        <v>-447</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flynas XY-273</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1535</v>
+        <v>1879</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-586</v>
+        <v>-317</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>flynas XY-275</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1603</v>
+        <v>1879</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-518</v>
+        <v>-317</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-416</t>
+          <t>flyadeal F3-611</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1648</v>
+        <v>1945</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-473</v>
+        <v>-251</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>30</v>
@@ -2282,9 +2282,9 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>flyadeal F3-607</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1729</v>
+        <v>1945</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-392</v>
+        <v>-251</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-252</t>
+          <t>flyadeal F3-605</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1843</v>
+        <v>1945</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-278</v>
+        <v>-251</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>30</v>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-287</t>
+          <t>flynas XY-271</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2069</v>
+        <v>2059</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-52</v>
+        <v>-137</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>40</v>
@@ -2431,36 +2431,36 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-265</t>
+          <t>Nesma Airlines NE-165</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2069</v>
+        <v>1535</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-52</v>
+        <v>-361</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2069</v>
+        <v>1539</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-52</v>
+        <v>-357</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2521,36 +2521,36 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-275</t>
+          <t>flynas XY-273</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2069</v>
+        <v>1539</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-52</v>
+        <v>-357</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2566,12 +2566,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2069</v>
+        <v>1539</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-52</v>
+        <v>-357</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2611,36 +2611,36 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-271</t>
+          <t>flynas XY-269</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2069</v>
+        <v>1539</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-52</v>
+        <v>-357</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2656,40 +2656,40 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SM-470</t>
+          <t>SM-462</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2069</v>
+        <v>1771</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2121</v>
+        <v>1896</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-52</v>
+        <v>-125</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1529</v>
+        <v>1843</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-892</v>
+        <v>-53</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>30</v>
@@ -2732,9 +2732,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1529</v>
+        <v>1843</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-892</v>
+        <v>-53</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>30</v>
@@ -2777,9 +2777,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1529</v>
+        <v>1843</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-892</v>
+        <v>-53</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,40 +2836,40 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>27-MAR-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-165</t>
+          <t>flynas XY-269</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-886</v>
+        <v>-357</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,27 +2881,27 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>27-MAR-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-163</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1535</v>
+        <v>1843</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-886</v>
+        <v>-53</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>30</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>27-MAR-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2940,13 +2940,13 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1535</v>
+        <v>1845</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-886</v>
+        <v>-51</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
@@ -2957,9 +2957,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>27-MAR-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1539</v>
+        <v>1892</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-882</v>
+        <v>-4</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>30</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-287</t>
+          <t>Nile Air NP-352</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1539</v>
+        <v>1843</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-882</v>
+        <v>-53</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,30 +3071,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-265</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1539</v>
+        <v>1843</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-882</v>
+        <v>-53</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-267</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1539</v>
+        <v>1845</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2421</v>
+        <v>1896</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-882</v>
+        <v>-51</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,40 +3151,40 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-275</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1539</v>
+        <v>1843</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-882</v>
+        <v>-353</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,40 +3196,40 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-271</t>
+          <t>Nile Air NP-254</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1539</v>
+        <v>1843</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-882</v>
+        <v>-353</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,40 +3241,40 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-611</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1749</v>
+        <v>1843</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-672</v>
+        <v>-353</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3286,40 +3286,40 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-615</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1749</v>
+        <v>1845</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-672</v>
+        <v>-351</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,27 +3331,27 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>flynas XY-265</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
         <v>1879</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-542</v>
+        <v>-317</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>20</v>
@@ -3362,9 +3362,9 @@
       <c r="I64" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,27 +3376,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-263</t>
+          <t>flynas XY-267</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
         <v>1879</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-542</v>
+        <v>-317</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>20</v>
@@ -3407,9 +3407,9 @@
       <c r="I65" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,27 +3421,27 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>flynas XY-273</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
         <v>1879</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-542</v>
+        <v>-317</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>20</v>
@@ -3452,9 +3452,9 @@
       <c r="I66" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,36 +3466,36 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-607</t>
+          <t>flynas XY-275</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1999</v>
+        <v>1879</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-422</v>
+        <v>-317</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
@@ -3511,36 +3511,36 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-605</t>
+          <t>flynas XY-263</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1999</v>
+        <v>1879</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-422</v>
+        <v>-317</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
@@ -3556,36 +3556,36 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>flynas XY-271</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2291</v>
+        <v>1879</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-130</v>
+        <v>-317</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
@@ -3601,36 +3601,36 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-313</t>
+          <t>flynas XY-269</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2291</v>
+        <v>1879</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-130</v>
+        <v>-317</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -3646,40 +3646,40 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-417</t>
+          <t>Nile Air NP-154</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2291</v>
+        <v>1843</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>2421</v>
+        <v>2196</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-130</v>
+        <v>-353</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,36 +3691,36 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-611</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1449</v>
+        <v>1843</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1889</v>
+        <v>2196</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-440</v>
+        <v>-353</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -3736,40 +3736,40 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-605</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1449</v>
+        <v>2144</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1889</v>
+        <v>2196</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-440</v>
+        <v>-52</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,40 +3781,40 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-615</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1449</v>
+        <v>1845</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-440</v>
+        <v>-726</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,27 +3826,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1464</v>
+        <v>2144</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-425</v>
+        <v>-427</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>30</v>
@@ -3871,27 +3871,27 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1529</v>
+        <v>2144</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-360</v>
+        <v>-427</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>30</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,27 +3916,27 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1535</v>
+        <v>2145</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-354</v>
+        <v>-426</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>30</v>
@@ -3947,9 +3947,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,40 +3961,40 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-287</t>
+          <t>flyadeal F3-613</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1539</v>
+        <v>2149</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-350</v>
+        <v>-422</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,40 +4006,40 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-265</t>
+          <t>flyadeal F3-607</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1539</v>
+        <v>2149</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-350</v>
+        <v>-422</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,40 +4051,40 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-267</t>
+          <t>flyadeal F3-605</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1539</v>
+        <v>2149</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-350</v>
+        <v>-422</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,40 +4096,40 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>flyadeal F3-615</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1539</v>
+        <v>2149</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-350</v>
+        <v>-422</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,27 +4141,27 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-275</t>
+          <t>flynas XY-265</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1539</v>
+        <v>2279</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-350</v>
+        <v>-292</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>20</v>
@@ -4172,9 +4172,9 @@
       <c r="I82" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,27 +4186,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-263</t>
+          <t>flynas XY-273</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1539</v>
+        <v>2279</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-350</v>
+        <v>-292</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>20</v>
@@ -4217,9 +4217,9 @@
       <c r="I83" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4231,40 +4231,40 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-271</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1539</v>
+        <v>2546</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-350</v>
+        <v>-25</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,36 +4276,36 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>Nile Air NP-254</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1729</v>
+        <v>2144</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-160</v>
+        <v>-427</v>
       </c>
       <c r="G85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H85" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="I85" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -4321,40 +4321,40 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SM-462</t>
+          <t>SM-470</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-417</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2115</v>
+        <v>2144</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1889</v>
+        <v>2571</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>226</v>
+        <v>-427</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,30 +4376,30 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Nesma Airlines NE-165</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1464</v>
+        <v>2145</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>1619</v>
+        <v>2571</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-155</v>
+        <v>-426</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,26 +4421,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>flyadeal F3-613</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1529</v>
+        <v>2149</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1619</v>
+        <v>2571</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-90</v>
+        <v>-422</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,26 +4466,26 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flyadeal F3-607</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1535</v>
+        <v>2149</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>1619</v>
+        <v>2571</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-84</v>
+        <v>-422</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,33 +4511,2283 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
+          <t>flyadeal F3-605</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-615</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-267</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>2199</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-372</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-275</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>2199</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-372</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-271</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>2199</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-372</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-152</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>2144</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-427</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-254</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>2144</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-427</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-163</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-426</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-613</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-607</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-615</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-605</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>2345</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-226</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-411</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>2346</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-225</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-165</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-1396</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-265</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-273</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-275</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-263</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-271</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
           <t>flynas XY-269</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>1729</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>1619</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G90" s="2" t="n">
+      <c r="D109" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H109" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="I109" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-254</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-1238</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-252</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-1238</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-161</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-1236</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-411</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-1198</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-607</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-1122</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-267</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1459</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-1112</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-605</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1749</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-822</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-615</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1749</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-822</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-613</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>2345</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-226</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>04-APR-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-159</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-265</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-332</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-273</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-332</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-263</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-332</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-271</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-332</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-269</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-332</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-165</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-296</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-252</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-198</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-411</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>-182</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>10-APR-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-265</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>759</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-63</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>10-APR-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>10-APR-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-462</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>726</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>12-APR-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>513</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>17-APR-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>654</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>17-APR-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-470</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>18-APR-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-462</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-161</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>513</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
